--- a/exemplos/modelo-SN/resultado_levantamento.xlsx
+++ b/exemplos/modelo-SN/resultado_levantamento.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Anexo II (notas selecionadas)'!$A$1:$AI$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumo por produto'!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Anexo II (notas selecionadas)'!$A$1:$AI$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumo por produto'!$A$1:$N$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pendências'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cliente: DROGARIA EXEMPLO LTDA</t>
+          <t>Cliente: COMERCIAL EXEMPLO LTDA</t>
         </is>
       </c>
     </row>
@@ -505,28 +505,28 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Itens triados: 5 (R$ 683,00 em estoque) | linhas de alocação: 6</t>
+          <t>Itens triados: 6 (R$ 4.251,00 em estoque) | linhas de alocação: 8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Situação da localização: Confirmado: 5</t>
+          <t>Situação da localização: Confirmado: 6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CRÉDITO TOTAL (Anexo V): R$ 50,22 em 5 mercadorias. É o valor do lançamento: soma de todo o crédito calculado pela fórmula do anexo, com as premissas e observações registradas.</t>
+          <t>CRÉDITO TOTAL (Anexo V): R$ 308,06 em 6 mercadorias. É o valor do lançamento: soma de todo o crédito calculado pela fórmula do anexo, com as premissas e observações registradas.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Composição: soma das linhas R$ 50,22 + ajuste do piso zero por mercadoria R$ 0,00 = R$ 50,22. Com VlMerc = vProd (sem descontar o desconto da nota) o crédito seria R$ 50,22.</t>
+          <t>Composição: soma das linhas R$ 308,06 + ajuste do piso zero por mercadoria R$ 0,00 = R$ 308,06. Com VlMerc = vProd (sem descontar o desconto da nota) o crédito seria R$ 308,06.</t>
         </is>
       </c>
     </row>
@@ -582,14 +582,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Entrada: só a data de emissão; sem registro de entrada: 6 (linhas de nota).</t>
+          <t>Entrada: só a data de emissão; sem registro de entrada: 8 (linhas de nota).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PONTOS EM ABERTO (não validados juridicamente; mostrados com o efeito): piso zero por mercadoria (ajuste R$ 0,00 no total); VlMerc líquido de desconto (com vProd o crédito seria R$ 50,22); FCP com base própria calculado em cada base; analogias do Anexo IV; a parcela do art. 3º, §4º (CAT 75/08) não é identificada nem deduzida.</t>
+          <t>PONTOS EM ABERTO (não validados juridicamente; mostrados com o efeito): piso zero por mercadoria (ajuste R$ 0,00 no total); VlMerc líquido de desconto (com vProd o crédito seria R$ 308,06); FCP com base própria calculado em cada base; analogias do Anexo IV; a parcela do art. 3º, §4º (CAT 75/08) não é identificada nem deduzida.</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1123,21 +1123,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LOSARTANA</t>
+          <t>LAMPADA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30049069</t>
+          <t>85395200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1300100</t>
+          <t>0900100</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1172,13 +1172,13 @@
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="N3" t="n">
-        <v>114.8</v>
+        <v>102.2</v>
       </c>
       <c r="P3" t="n">
-        <v>5.9</v>
+        <v>5.26</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>LOSARTANA POTASSICA 50MG C/30 COMP</t>
+          <t>LAMPADA LED BULBO 9W BIVOLT</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>descrição com dose/forma farmacêutica e NCM de medicamento; CEST da nota 13.001.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
+          <t>termo da descrição legal na descrição do produto: LAMPA; CEST da nota 09.001.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOSARTANA</t>
+          <t>LAMPADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30049069</t>
+          <t>85395200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1300100</t>
+          <t>0900100</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>168</v>
+        <v>490</v>
       </c>
       <c r="P4" t="n">
-        <v>8.640000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>LOSARTANA POTASSICA 50MG C/30 COMP</t>
+          <t>LAMPADA LED BULBO 9W BIVOLT</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -1336,28 +1336,28 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>descrição com dose/forma farmacêutica e NCM de medicamento; CEST da nota 13.001.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
+          <t>termo da descrição legal na descrição do produto: LAMPA; CEST da nota 09.001.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>SUCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30049069</t>
+          <t>20096100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1300100</t>
+          <t>1701000</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1389,16 +1389,16 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="N5" t="n">
-        <v>252</v>
+        <v>319.2</v>
       </c>
       <c r="P5" t="n">
-        <v>12.96</v>
+        <v>16.42</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>PARACETAMOL 750MG C/20 COMP</t>
+          <t>SUCO DE UVA INTEGRAL 1L</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1446,24 +1446,28 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>descrição com dose/forma farmacêutica e NCM de medicamento; CEST da nota 13.001.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
+          <t>termo da descrição legal na descrição do produto: SUCO; CEST da nota 17.010.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAMADEIRA</t>
+          <t>SUCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>39241000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>20096100</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1701000</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1484,7 +1488,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1495,16 +1499,16 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M6" t="n">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="N6" t="n">
-        <v>117.6</v>
+        <v>302.4</v>
       </c>
       <c r="P6" t="n">
-        <v>6.05</v>
+        <v>15.55</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1519,21 +1523,21 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7890000000046</t>
+          <t>7890000000039</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>MAMADEIRA BICO DE SILICONE 240ML</t>
+          <t>SUCO DE UVA INTEGRAL 1L</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1552,7 +1556,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>termo da descrição legal na descrição do produto: MAMAD; exclusão: Portaria SRE-94/25 com efeito em 01/04/2026</t>
+          <t>termo da descrição legal na descrição do produto: SUCO; CEST da nota 17.010.00 igual ao do item; exclusão: Portaria SRE-64/25 com efeito em 01/01/2026</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1629,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7890000000053</t>
+          <t>7890000000046</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1662,8 +1666,228 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TINTA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>32091010</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2400100</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>35260822222222000122550010000010051079585953</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1260</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1764</v>
+      </c>
+      <c r="P8" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>C = (BC ST - VlMerc) x Alíquota interna</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Anexo V: SN, sem redução</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7890000000053</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TINTA ACRILICA FOSCA BRANCA 18L</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1260</v>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ST da nota (pICMSST + pFCPST)</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>só a data de emissão; sem registro de entrada</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>termo da descrição legal na descrição do produto: TINTA; CEST da nota 24.001.00 igual ao do item; exclusão: Portaria SRE-34/26 com efeito em 01/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PNEU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>40111000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1600100</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>35260822222222000122550010000010051079585953</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1920</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2688</v>
+      </c>
+      <c r="P9" t="n">
+        <v>138.24</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>C = (BC ST - VlMerc) x Alíquota interna</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Anexo V: SN, sem redução</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7890000000060</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>PNEU NOVO ARO 15 195/60R15</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1920</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ST da nota (pICMSST + pFCPST)</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>só a data de emissão; sem registro de entrada</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>termo da descrição legal na descrição do produto: NOVO, PNEU; CEST da nota 16.001.00 igual ao do item; exclusão: Portaria SRE-34/26 com efeito em 01/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI7"/>
+  <autoFilter ref="A1:AI9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1674,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1820,7 +2044,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LOSARTANA</t>
+          <t>LAMPADA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1830,7 +2054,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOSARTANA POTASSICA 50MG C/30 COMP</t>
+          <t>LAMPADA LED BULBO 9W BIVOLT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1839,25 +2063,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>202</v>
+        <v>423</v>
       </c>
       <c r="G3" t="n">
-        <v>282.8</v>
+        <v>592.2</v>
       </c>
       <c r="H3" t="n">
-        <v>14.54</v>
+        <v>30.46</v>
       </c>
       <c r="I3" t="n">
-        <v>8.08</v>
+        <v>7.05</v>
       </c>
       <c r="J3" t="n">
-        <v>11.312</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5816</v>
+        <v>0.5077</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1872,7 +2096,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>SUCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1882,7 +2106,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PARACETAMOL 750MG C/20 COMP</t>
+          <t>SUCO DE UVA INTEGRAL 1L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1891,25 +2115,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>180</v>
+        <v>444</v>
       </c>
       <c r="G4" t="n">
-        <v>252</v>
+        <v>621.6</v>
       </c>
       <c r="H4" t="n">
-        <v>12.96</v>
+        <v>31.97</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>9.25</v>
       </c>
       <c r="J4" t="n">
-        <v>8.4</v>
+        <v>12.95</v>
       </c>
       <c r="K4" t="n">
-        <v>0.432</v>
+        <v>0.666</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1924,7 +2148,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAMADEIRA</t>
+          <t>SHAMPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1934,7 +2158,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MAMADEIRA BICO DE SILICONE 240ML</t>
+          <t>SHAMPOO ANTICASPA 400ML</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1943,25 +2167,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>103.5</v>
       </c>
       <c r="G5" t="n">
-        <v>117.6</v>
+        <v>144.9</v>
       </c>
       <c r="H5" t="n">
-        <v>6.05</v>
+        <v>7.45</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>19.6</v>
+        <v>16.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0083</v>
+        <v>0.8278</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1976,7 +2200,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SHAMPOO</t>
+          <t>TINTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1986,34 +2210,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SHAMPOO ANTICASPA 400ML</t>
+          <t>TINTA ACRILICA FOSCA BRANCA 18L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>103.5</v>
+        <v>1260</v>
       </c>
       <c r="G6" t="n">
-        <v>144.9</v>
+        <v>1764</v>
       </c>
       <c r="H6" t="n">
-        <v>7.45</v>
+        <v>90.72</v>
       </c>
       <c r="I6" t="n">
-        <v>11.5</v>
+        <v>180</v>
       </c>
       <c r="J6" t="n">
-        <v>16.1</v>
+        <v>252</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8278</v>
+        <v>12.96</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2025,8 +2249,60 @@
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PNEU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7890000000060</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PNEU NOVO ARO 15 195/60R15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2688</v>
+      </c>
+      <c r="H7" t="n">
+        <v>138.24</v>
+      </c>
+      <c r="I7" t="n">
+        <v>320</v>
+      </c>
+      <c r="J7" t="n">
+        <v>448</v>
+      </c>
+      <c r="K7" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2037,7 +2313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2092,7 +2368,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.72</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2398,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.5</v>
+        <v>7.45</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2135,6 +2411,36 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>1 mercadorias com crédito. O que exceder o ICMS devido do mês compensa nos meses seguintes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>única</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>228.96</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dedução do ICMS devido no PGDAS-D (campo "redução da base de cálculo"), no mês posterior ao da exclusão</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>2 mercadorias com crédito. O que exceder o ICMS devido do mês compensa nos meses seguintes.</t>
         </is>

--- a/exemplos/modelo-SN/resultado_levantamento.xlsx
+++ b/exemplos/modelo-SN/resultado_levantamento.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Anexo II (notas selecionadas)'!$A$1:$AI$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumo por produto'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Anexo II (notas selecionadas)'!$A$1:$AI$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumo por produto'!$A$1:$N$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pendências'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,28 +505,28 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Itens triados: 6 (R$ 4.251,00 em estoque) | linhas de alocação: 8</t>
+          <t>Itens triados: 8 (R$ 4.446,00 em estoque) | linhas de alocação: 11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Situação da localização: Confirmado: 6</t>
+          <t>Situação da localização: Confirmado: 8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CRÉDITO TOTAL (Anexo V): R$ 308,06 em 6 mercadorias. É o valor do lançamento: soma de todo o crédito calculado pela fórmula do anexo, com as premissas e observações registradas.</t>
+          <t>CRÉDITO TOTAL (Anexo V): R$ 322,14 em 8 mercadorias. É o valor do lançamento: soma de todo o crédito calculado pela fórmula do anexo, com as premissas e observações registradas.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Composição: soma das linhas R$ 308,06 + ajuste do piso zero por mercadoria R$ 0,00 = R$ 308,06. Com VlMerc = vProd (sem descontar o desconto da nota) o crédito seria R$ 308,06.</t>
+          <t>Composição: soma das linhas R$ 322,14 + ajuste do piso zero por mercadoria R$ 0,00 = R$ 322,14. Com VlMerc = vProd (sem descontar o desconto da nota) o crédito seria R$ 322,14.</t>
         </is>
       </c>
     </row>
@@ -582,14 +582,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Entrada: só a data de emissão; sem registro de entrada: 8 (linhas de nota).</t>
+          <t>Entrada: só a data de emissão; sem registro de entrada: 11 (linhas de nota).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PONTOS EM ABERTO (não validados juridicamente; mostrados com o efeito): piso zero por mercadoria (ajuste R$ 0,00 no total); VlMerc líquido de desconto (com vProd o crédito seria R$ 308,06); FCP com base própria calculado em cada base; analogias do Anexo IV; a parcela do art. 3º, §4º (CAT 75/08) não é identificada nem deduzida.</t>
+          <t>PONTOS EM ABERTO (não validados juridicamente; mostrados com o efeito): piso zero por mercadoria (ajuste R$ 0,00 no total); VlMerc líquido de desconto (com vProd o crédito seria R$ 322,14); FCP com base própria calculado em cada base; analogias do Anexo IV; a parcela do art. 3º, §4º (CAT 75/08) não é identificada nem deduzida.</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1605,16 +1605,16 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>103.5</v>
+        <v>115</v>
       </c>
       <c r="N7" t="n">
-        <v>144.9</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
-        <v>7.45</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>103.5</v>
+        <v>115</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1669,21 +1669,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TINTA</t>
+          <t>SHAMPOO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32091010</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2400100</t>
-        </is>
-      </c>
+          <t>33051000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1695,16 +1691,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>35260822222222000122550010000010051079585953</t>
+          <t>35251211111111000111550010000010021079348380</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1715,16 +1711,16 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>1260</v>
+        <v>66</v>
       </c>
       <c r="N8" t="n">
-        <v>1764</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>90.72</v>
+        <v>4.75</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1739,21 +1735,21 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7890000000053</t>
+          <t>7890000000046</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>TINTA ACRILICA FOSCA BRANCA 18L</t>
+          <t>SHAMPOO ANTICASPA 400ML</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>1260</v>
+        <v>66</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1761,7 +1757,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ST da nota (pICMSST + pFCPST)</t>
+          <t>ST retido anteriormente (pST, já inclui FCP)</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1772,28 +1768,28 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>termo da descrição legal na descrição do produto: TINTA; CEST da nota 24.001.00 igual ao do item; exclusão: Portaria SRE-34/26 com efeito em 01/10/2026</t>
+          <t>termo da descrição legal na descrição do produto: XAMPU; exclusão: Portaria SRE-94/25 com efeito em 01/04/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PNEU</t>
+          <t>SORVETE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>40111000</t>
+          <t>21050010</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1600100</t>
+          <t>2300100</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1805,16 +1801,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>35260822222222000122550010000010051079585953</t>
+          <t>35260611111111000111550010000010061079665140</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1825,16 +1821,16 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>1920</v>
+        <v>288</v>
       </c>
       <c r="N9" t="n">
-        <v>2688</v>
+        <v>403.2</v>
       </c>
       <c r="P9" t="n">
-        <v>138.24</v>
+        <v>20.74</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1849,21 +1845,21 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7890000000060</t>
+          <t>7890000000077</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>PNEU NOVO ARO 15 195/60R15</t>
+          <t>SORVETE CREMOSO CHOCOLATE 2L</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>1920</v>
+        <v>288</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1871,7 +1867,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ST da nota (pICMSST + pFCPST)</t>
+          <t>ST retido anteriormente (pST, já inclui FCP)</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1882,12 +1878,342 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
+          <t>termo da descrição legal na descrição do produto: SORVE; CEST da nota 23.001.00 igual ao do item; exclusão: Portaria SRE-09/26 com efeito em 01/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FERRO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>85164000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2104400</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>35260722222222000122550010000010071079744335</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>650</v>
+      </c>
+      <c r="N10" t="n">
+        <v>910</v>
+      </c>
+      <c r="P10" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>C = (BC ST - VlMerc) x Alíquota interna</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Anexo V: SN, sem redução</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7890000000084</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>FERRO ELETRICO A VAPOR 1200W</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>650</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ST da nota (pICMSST + pFCPST)</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>só a data de emissão; sem registro de entrada</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>termo da descrição legal na descrição do produto: ELETR, FERRO; CEST da nota 21.044.00 igual ao do item; exclusão: Portaria SRE-19/26 com efeito em 01/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TINTA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>32091010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2400100</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>35260822222222000122550010000010051079585953</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1080</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1512</v>
+      </c>
+      <c r="P11" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>C = (BC ST - VlMerc) x Alíquota interna</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Anexo V: SN, sem redução</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7890000000053</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>TINTA ACRILICA FOSCA BRANCA 18L</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ST da nota (pICMSST + pFCPST)</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>só a data de emissão; sem registro de entrada</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>termo da descrição legal na descrição do produto: TINTA; CEST da nota 24.001.00 igual ao do item; exclusão: Portaria SRE-34/26 com efeito em 01/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PNEU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>40111000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1600100</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>35260822222222000122550010000010051079585953</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1280</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1792</v>
+      </c>
+      <c r="P12" t="n">
+        <v>92.16</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>C = (BC ST - VlMerc) x Alíquota interna</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Anexo V: SN, sem redução</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>7890000000060</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PNEU NOVO ARO 15 195/60R15</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ST da nota (pICMSST + pFCPST)</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>só a data de emissão; sem registro de entrada</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>termo da descrição legal na descrição do produto: NOVO, PNEU; CEST da nota 16.001.00 igual ao do item; exclusão: Portaria SRE-34/26 com efeito em 01/10/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI9"/>
+  <autoFilter ref="A1:AI12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1898,7 +2224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2167,25 +2493,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>103.5</v>
+        <v>181</v>
       </c>
       <c r="G5" t="n">
-        <v>144.9</v>
+        <v>253.4</v>
       </c>
       <c r="H5" t="n">
-        <v>7.45</v>
+        <v>13.03</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5</v>
+        <v>11.3125</v>
       </c>
       <c r="J5" t="n">
-        <v>16.1</v>
+        <v>15.8375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8278</v>
+        <v>0.8144</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2200,44 +2526,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TINTA</t>
+          <t>SORVETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7890000000053</t>
+          <t>7890000000077</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TINTA ACRILICA FOSCA BRANCA 18L</t>
+          <t>SORVETE CREMOSO CHOCOLATE 2L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>1260</v>
+        <v>288</v>
       </c>
       <c r="G6" t="n">
-        <v>1764</v>
+        <v>403.2</v>
       </c>
       <c r="H6" t="n">
-        <v>90.72</v>
+        <v>20.74</v>
       </c>
       <c r="I6" t="n">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>252</v>
+        <v>25.2</v>
       </c>
       <c r="K6" t="n">
-        <v>12.96</v>
+        <v>1.2962</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2252,44 +2578,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PNEU</t>
+          <t>FERRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7890000000060</t>
+          <t>7890000000084</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PNEU NOVO ARO 15 195/60R15</t>
+          <t>FERRO ELETRICO A VAPOR 1200W</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>1920</v>
+        <v>650</v>
       </c>
       <c r="G7" t="n">
-        <v>2688</v>
+        <v>910</v>
       </c>
       <c r="H7" t="n">
-        <v>138.24</v>
+        <v>46.8</v>
       </c>
       <c r="I7" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="J7" t="n">
-        <v>448</v>
+        <v>91</v>
       </c>
       <c r="K7" t="n">
-        <v>23.04</v>
+        <v>4.68</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2301,8 +2627,112 @@
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TINTA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7890000000053</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TINTA ACRILICA FOSCA BRANCA 18L</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1512</v>
+      </c>
+      <c r="H8" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>180</v>
+      </c>
+      <c r="J8" t="n">
+        <v>252</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PNEU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7890000000060</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PNEU NOVO ARO 15 195/60R15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1792</v>
+      </c>
+      <c r="H9" t="n">
+        <v>92.16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>320</v>
+      </c>
+      <c r="J9" t="n">
+        <v>448</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N7"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2313,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2398,7 +2828,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.45</v>
+        <v>13.03</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2419,28 +2849,88 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>única</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dedução do ICMS devido no PGDAS-D (campo "redução da base de cálculo"), no mês posterior ao da exclusão</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1 mercadorias com crédito. O que exceder o ICMS devido do mês compensa nos meses seguintes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>única</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Simples Nacional</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dedução do ICMS devido no PGDAS-D (campo "redução da base de cálculo"), no mês posterior ao da exclusão</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1 mercadorias com crédito. O que exceder o ICMS devido do mês compensa nos meses seguintes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>11/2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>única</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>228.96</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C6" t="n">
+        <v>169.92</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Simples Nacional</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Dedução do ICMS devido no PGDAS-D (campo "redução da base de cálculo"), no mês posterior ao da exclusão</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2 mercadorias com crédito. O que exceder o ICMS devido do mês compensa nos meses seguintes.</t>
         </is>
